--- a/微程序.xlsx
+++ b/微程序.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nhjk/Sdu/COA/exp3_source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB265DAB-EB9C-B94F-8E2C-0480D596F666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BBB903-0604-064D-82EE-4C5C3F39A4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="226">
   <si>
     <t>微操作</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1252,6 +1252,118 @@
   </si>
   <si>
     <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>81</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>41</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">00 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>78</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>58</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>61</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>08</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1394,7 +1506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1430,6 +1542,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1855,6 +1970,15 @@
       <c r="M4" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="N4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="32">
       <c r="B5" s="5" t="s">
@@ -1893,6 +2017,15 @@
       <c r="M5" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="N5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="4" t="s">
@@ -1931,6 +2064,15 @@
       <c r="M6" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="N6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="7" spans="1:16">
       <c r="B7" s="4" t="s">
@@ -1969,6 +2111,15 @@
       <c r="M7" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="N7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="4" t="s">
@@ -2012,6 +2163,15 @@
       <c r="M9" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="N9" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="32">
       <c r="B10" s="5" t="s">
@@ -2050,6 +2210,15 @@
       <c r="M10" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="N10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="B11" s="4" t="s">
@@ -2088,6 +2257,15 @@
       <c r="M11" s="4" t="s">
         <v>49</v>
       </c>
+      <c r="N11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="4" t="s">
@@ -2126,6 +2304,15 @@
       <c r="M13" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="N13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="14" spans="1:16">
       <c r="B14" s="4" t="s">
@@ -2164,6 +2351,15 @@
       <c r="M14" s="4" t="s">
         <v>46</v>
       </c>
+      <c r="N14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="4" t="s">
@@ -2202,8 +2398,17 @@
       <c r="M16" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="B17" s="4" t="s">
         <v>57</v>
       </c>
@@ -2240,8 +2445,17 @@
       <c r="M17" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="B19" s="4" t="s">
         <v>59</v>
       </c>
@@ -2278,8 +2492,17 @@
       <c r="M19" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="B20" s="4" t="s">
         <v>57</v>
       </c>
@@ -2316,13 +2539,22 @@
       <c r="M20" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:16">
       <c r="B22" s="4" t="s">
         <v>31</v>
       </c>
@@ -2359,8 +2591,17 @@
       <c r="M22" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" ht="32">
+      <c r="N22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="32">
       <c r="B23" s="5" t="s">
         <v>33</v>
       </c>
@@ -2397,8 +2638,17 @@
       <c r="M23" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="B24" s="4" t="s">
         <v>66</v>
       </c>
@@ -2435,8 +2685,17 @@
       <c r="M24" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" ht="16">
+      <c r="N24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="16">
       <c r="B25" s="5" t="s">
         <v>32</v>
       </c>
@@ -2473,8 +2732,17 @@
       <c r="M25" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="B26" s="4" t="s">
         <v>48</v>
       </c>
@@ -2511,13 +2779,22 @@
       <c r="M26" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:16">
       <c r="B28" s="4" t="s">
         <v>72</v>
       </c>
@@ -2554,8 +2831,17 @@
       <c r="M28" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="N28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="B29" s="4" t="s">
         <v>73</v>
       </c>
@@ -2592,8 +2878,17 @@
       <c r="M29" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="B30" s="4" t="s">
         <v>74</v>
       </c>
@@ -2630,8 +2925,17 @@
       <c r="M30" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="N30" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="B31" s="4" t="s">
         <v>57</v>
       </c>
@@ -2668,8 +2972,17 @@
       <c r="M31" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="N31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" s="4" t="s">
         <v>86</v>
       </c>
@@ -2904,6 +3217,15 @@
       <c r="M38" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="N38" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="39" spans="1:16">
       <c r="B39" s="7" t="s">
@@ -2942,6 +3264,15 @@
       <c r="M39" s="6" t="s">
         <v>26</v>
       </c>
+      <c r="N39" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="40" spans="1:16">
       <c r="B40" s="7" t="s">
@@ -2980,6 +3311,15 @@
       <c r="M40" s="6" t="s">
         <v>80</v>
       </c>
+      <c r="N40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="41" spans="1:16">
       <c r="B41" s="1" t="s">
@@ -3018,6 +3358,15 @@
       <c r="M41" s="2" t="s">
         <v>81</v>
       </c>
+      <c r="N41" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O41" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="4" t="s">
@@ -3061,6 +3410,15 @@
       <c r="M43" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="N43" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="44" spans="1:16">
       <c r="B44" s="7" t="s">
@@ -3099,6 +3457,15 @@
       <c r="M44" s="6" t="s">
         <v>26</v>
       </c>
+      <c r="N44" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="45" spans="1:16">
       <c r="B45" s="7" t="s">
@@ -3137,6 +3504,15 @@
       <c r="M45" s="6" t="s">
         <v>80</v>
       </c>
+      <c r="N45" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="46" spans="1:16">
       <c r="B46" s="1" t="s">
@@ -3175,6 +3551,15 @@
       <c r="M46" s="2" t="s">
         <v>81</v>
       </c>
+      <c r="N46" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="4" t="s">
@@ -3218,8 +3603,17 @@
       <c r="M48" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="N48" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
       <c r="B49" s="7" t="s">
         <v>120</v>
       </c>
@@ -3256,8 +3650,17 @@
       <c r="M49" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="50" spans="1:13">
+      <c r="N49" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
       <c r="B50" s="7" t="s">
         <v>90</v>
       </c>
@@ -3294,8 +3697,17 @@
       <c r="M50" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="51" spans="1:13">
+      <c r="N50" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
       <c r="B51" s="1" t="s">
         <v>91</v>
       </c>
@@ -3332,13 +3744,22 @@
       <c r="M51" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="52" spans="1:13">
+      <c r="N51" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:16">
       <c r="B53" s="4" t="s">
         <v>127</v>
       </c>
@@ -3375,8 +3796,17 @@
       <c r="M53" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="54" spans="1:13">
+      <c r="N53" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="P53" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="B54" s="4" t="s">
         <v>153</v>
       </c>
@@ -3413,8 +3843,17 @@
       <c r="M54" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="55" spans="1:13">
+      <c r="N54" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="P54" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
       <c r="B55" s="4" t="s">
         <v>128</v>
       </c>
@@ -3451,8 +3890,17 @@
       <c r="M55" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="56" spans="1:13">
+      <c r="N55" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O55" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P55" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
       <c r="B56" s="4" t="s">
         <v>57</v>
       </c>
@@ -3489,13 +3937,22 @@
       <c r="M56" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="57" spans="1:13">
+      <c r="N56" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
       <c r="A57" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:16">
       <c r="B58" s="4" t="s">
         <v>127</v>
       </c>
@@ -3532,8 +3989,17 @@
       <c r="M58" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="59" spans="1:13">
+      <c r="N58" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O58" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="P58" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
       <c r="B59" s="4" t="s">
         <v>152</v>
       </c>
@@ -3570,8 +4036,17 @@
       <c r="M59" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="60" spans="1:13">
+      <c r="N59" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="O59" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="P59" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
       <c r="B60" s="4" t="s">
         <v>128</v>
       </c>
@@ -3608,8 +4083,17 @@
       <c r="M60" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="61" spans="1:13">
+      <c r="N60" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O60" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P60" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
       <c r="B61" s="4" t="s">
         <v>57</v>
       </c>
@@ -3646,13 +4130,22 @@
       <c r="M61" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="62" spans="1:13">
+      <c r="N61" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O61" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P61" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
       <c r="A62" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:16">
       <c r="B63" s="1" t="s">
         <v>88</v>
       </c>
@@ -3689,8 +4182,17 @@
       <c r="M63" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="64" spans="1:13">
+      <c r="N63" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O63" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="P63" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
       <c r="B64" s="7" t="s">
         <v>140</v>
       </c>
@@ -3727,8 +4229,17 @@
       <c r="M64" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="65" spans="1:13">
+      <c r="N64" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="O64" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="P64" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
       <c r="B65" s="7" t="s">
         <v>90</v>
       </c>
@@ -3765,8 +4276,17 @@
       <c r="M65" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="66" spans="1:13">
+      <c r="N65" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O65" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P65" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
       <c r="B66" s="1" t="s">
         <v>91</v>
       </c>
@@ -3803,13 +4323,22 @@
       <c r="M66" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="67" spans="1:13">
+      <c r="N66" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O66" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P66" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
       <c r="A67" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:16">
       <c r="B68" s="1" t="s">
         <v>88</v>
       </c>
@@ -3846,8 +4375,17 @@
       <c r="M68" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="69" spans="1:13">
+      <c r="N68" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O68" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="P68" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
       <c r="B69" s="7" t="s">
         <v>146</v>
       </c>
@@ -3884,8 +4422,17 @@
       <c r="M69" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="70" spans="1:13">
+      <c r="N69" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="O69" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="P69" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
       <c r="B70" s="7" t="s">
         <v>90</v>
       </c>
@@ -3922,8 +4469,17 @@
       <c r="M70" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="71" spans="1:13">
+      <c r="N70" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O70" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P70" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
       <c r="B71" s="1" t="s">
         <v>91</v>
       </c>
@@ -3960,13 +4516,22 @@
       <c r="M71" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="72" spans="1:13">
+      <c r="N71" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O71" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P71" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
       <c r="A72" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:16">
       <c r="B73" s="1" t="s">
         <v>88</v>
       </c>
@@ -4003,8 +4568,17 @@
       <c r="M73" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="74" spans="1:13">
+      <c r="N73" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O73" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="P73" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
       <c r="B74" s="7" t="s">
         <v>149</v>
       </c>
@@ -4041,8 +4615,17 @@
       <c r="M74" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="75" spans="1:13">
+      <c r="N74" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="O74" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="P74" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
       <c r="B75" s="7" t="s">
         <v>90</v>
       </c>
@@ -4079,8 +4662,17 @@
       <c r="M75" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="76" spans="1:13">
+      <c r="N75" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O75" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P75" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
       <c r="B76" s="1" t="s">
         <v>91</v>
       </c>
@@ -4117,13 +4709,22 @@
       <c r="M76" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="77" spans="1:13">
+      <c r="N76" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O76" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P76" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
       <c r="A77" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:16">
       <c r="B78" s="1" t="s">
         <v>154</v>
       </c>
@@ -4160,8 +4761,17 @@
       <c r="M78" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="79" spans="1:13">
+      <c r="N78" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O78" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="P78" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
       <c r="B79" s="7" t="s">
         <v>155</v>
       </c>
@@ -4198,8 +4808,17 @@
       <c r="M79" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="80" spans="1:13">
+      <c r="N79" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="O79" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="P79" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
       <c r="B80" s="7" t="s">
         <v>90</v>
       </c>
@@ -4236,8 +4855,17 @@
       <c r="M80" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="81" spans="1:13">
+      <c r="N80" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O80" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P80" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16">
       <c r="B81" s="1" t="s">
         <v>91</v>
       </c>
@@ -4274,13 +4902,22 @@
       <c r="M81" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="82" spans="1:13">
+      <c r="N81" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O81" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P81" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16">
       <c r="A82" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:16">
       <c r="B83" s="1" t="s">
         <v>88</v>
       </c>
@@ -4317,8 +4954,17 @@
       <c r="M83" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="84" spans="1:13">
+      <c r="N83" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O83" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="P83" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
       <c r="B84" s="7" t="s">
         <v>158</v>
       </c>
@@ -4355,8 +5001,17 @@
       <c r="M84" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="85" spans="1:13">
+      <c r="N84" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="O84" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="P84" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16">
       <c r="B85" s="7" t="s">
         <v>90</v>
       </c>
@@ -4393,8 +5048,17 @@
       <c r="M85" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="86" spans="1:13">
+      <c r="N85" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O85" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P85" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16">
       <c r="B86" s="1" t="s">
         <v>91</v>
       </c>
@@ -4431,13 +5095,22 @@
       <c r="M86" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="87" spans="1:13">
+      <c r="N86" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O86" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P86" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16">
       <c r="A87" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:16">
       <c r="B88" s="1" t="s">
         <v>88</v>
       </c>
@@ -4474,8 +5147,17 @@
       <c r="M88" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="89" spans="1:13">
+      <c r="N88" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O88" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="P88" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
       <c r="B89" s="7" t="s">
         <v>164</v>
       </c>
@@ -4512,8 +5194,17 @@
       <c r="M89" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="90" spans="1:13">
+      <c r="N89" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="O89" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="P89" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16">
       <c r="B90" s="7" t="s">
         <v>90</v>
       </c>
@@ -4550,8 +5241,17 @@
       <c r="M90" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="91" spans="1:13">
+      <c r="N90" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O90" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P90" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
       <c r="B91" s="1" t="s">
         <v>91</v>
       </c>
@@ -4588,13 +5288,22 @@
       <c r="M91" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="92" spans="1:13">
+      <c r="N91" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O91" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P91" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
       <c r="A92" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:16">
       <c r="B93" s="1" t="s">
         <v>88</v>
       </c>
@@ -4631,8 +5340,17 @@
       <c r="M93" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="94" spans="1:13">
+      <c r="N93" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O93" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="P93" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
       <c r="B94" s="7" t="s">
         <v>167</v>
       </c>
@@ -4669,8 +5387,17 @@
       <c r="M94" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="95" spans="1:13">
+      <c r="N94" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="O94" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="P94" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
       <c r="B95" s="7" t="s">
         <v>90</v>
       </c>
@@ -4707,8 +5434,17 @@
       <c r="M95" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="96" spans="1:13">
+      <c r="N95" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O95" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P95" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16">
       <c r="B96" s="1" t="s">
         <v>91</v>
       </c>
@@ -4745,13 +5481,22 @@
       <c r="M96" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="97" spans="1:13">
+      <c r="N96" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="O96" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P96" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
       <c r="A97" s="4" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:16">
       <c r="B98" s="4" t="s">
         <v>31</v>
       </c>
@@ -4788,8 +5533,17 @@
       <c r="M98" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="99" spans="1:13" ht="32">
+      <c r="N98" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O98" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="P98" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="32">
       <c r="B99" s="5" t="s">
         <v>33</v>
       </c>
@@ -4826,8 +5580,17 @@
       <c r="M99" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="100" spans="1:13">
+      <c r="N99" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O99" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="P99" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
       <c r="B100" s="4" t="s">
         <v>196</v>
       </c>
@@ -4864,8 +5627,17 @@
       <c r="M100" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="101" spans="1:13">
+      <c r="N100" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O100" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="P100" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
       <c r="B101" s="4" t="s">
         <v>57</v>
       </c>
@@ -4902,13 +5674,22 @@
       <c r="M101" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="102" spans="1:13">
+      <c r="N101" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O101" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P101" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
       <c r="A102" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:16">
       <c r="B103" s="4" t="s">
         <v>195</v>
       </c>
@@ -4944,6 +5725,15 @@
       </c>
       <c r="M103" s="6" t="s">
         <v>84</v>
+      </c>
+      <c r="N103" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O103" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P103" s="4" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/微程序.xlsx
+++ b/微程序.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nhjk/Sdu/COA/exp3_source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BBB903-0604-064D-82EE-4C5C3F39A4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF256D9-C4F8-9947-8AC1-5F9F1858E7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="258">
   <si>
     <t>微操作</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1364,6 +1364,134 @@
   </si>
   <si>
     <t>08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00E181</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000A11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00C041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00C081</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00C101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00C181</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000211</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>008181</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0041C1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>004141</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>266401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00A081</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>186401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0C6401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>306401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3E0401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6C6401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>786401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>586401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>006141</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7C0401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>506401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4C6401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00D001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00C0C1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1529,6 +1657,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1542,9 +1673,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1827,3920 +1955,4157 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P103"/>
+  <dimension ref="A1:Q103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" style="4"/>
-    <col min="4" max="4" width="30" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" style="4"/>
-    <col min="6" max="6" width="19.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="11.1640625" style="4" customWidth="1"/>
-    <col min="8" max="9" width="8.6640625" style="4"/>
-    <col min="10" max="10" width="17.33203125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" style="4"/>
-    <col min="13" max="13" width="10.6640625" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="8.6640625" style="4"/>
+    <col min="1" max="2" width="10.83203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="4"/>
+    <col min="5" max="5" width="30" style="4" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" style="4"/>
+    <col min="7" max="7" width="19.33203125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" style="4" customWidth="1"/>
+    <col min="9" max="10" width="8.6640625" style="4"/>
+    <col min="11" max="11" width="17.33203125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" style="4"/>
+    <col min="14" max="14" width="10.6640625" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="17">
+    <row r="1" spans="1:17" ht="17">
       <c r="A1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="9"/>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="10"/>
+      <c r="O1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="11"/>
       <c r="P1" s="12"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="B2" s="2"/>
+      <c r="Q1" s="13"/>
+    </row>
+    <row r="2" spans="1:17">
       <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="O2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="11"/>
       <c r="P2" s="12"/>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="13"/>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:17">
       <c r="B4" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L4" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="32">
-      <c r="B5" s="5" t="s">
+    <row r="5" spans="1:17" ht="32">
+      <c r="B5" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="I5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="M5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="Q5" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:17">
       <c r="B6" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H6" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L6" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="Q6" s="4" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:17">
       <c r="B7" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H7" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L7" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="N7" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O7" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q7" s="4" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:17">
       <c r="A8" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:17">
       <c r="B9" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H9" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L9" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="O9" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="P9" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="Q9" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="32">
-      <c r="B10" s="5" t="s">
+    <row r="10" spans="1:17" ht="32">
+      <c r="B10" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="I10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="K10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="L10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="M10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N10" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P10" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="P10" s="4" t="s">
+      <c r="Q10" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:17">
       <c r="B11" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H11" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L11" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="N11" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O11" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q11" s="4" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:17">
       <c r="B13" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L13" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N13" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P13" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="P13" s="4" t="s">
+      <c r="Q13" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:17">
       <c r="B14" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H14" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L14" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="N14" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O14" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q14" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:17">
       <c r="B16" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H16" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="K16" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L16" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N16" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="P16" s="4" t="s">
+      <c r="Q16" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:17">
       <c r="B17" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H17" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K17" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L17" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="N17" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O17" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q17" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:17">
       <c r="B19" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H19" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K19" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="K19" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L19" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N19" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P19" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="P19" s="4" t="s">
+      <c r="Q19" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:17">
       <c r="B20" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H20" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L20" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N20" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="N20" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O20" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q20" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:17">
       <c r="A21" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:17">
       <c r="B22" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H22" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K22" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L22" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N22" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P22" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="P22" s="4" t="s">
+      <c r="Q22" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="32">
-      <c r="B23" s="5" t="s">
+    <row r="23" spans="1:17" ht="32">
+      <c r="B23" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F23" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="H23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="I23" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="K23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="L23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="M23" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N23" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P23" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="P23" s="4" t="s">
+      <c r="Q23" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:17">
       <c r="B24" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H24" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K24" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K24" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L24" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N24" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P24" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="P24" s="4" t="s">
+      <c r="Q24" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="16">
-      <c r="B25" s="5" t="s">
+    <row r="25" spans="1:17" ht="16">
+      <c r="B25" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F25" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H25" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I25" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J25" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="K25" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K25" s="4" t="s">
+      <c r="L25" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="L25" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="M25" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N25" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P25" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="P25" s="4" t="s">
+      <c r="Q25" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:17">
       <c r="B26" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F26" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H26" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J26" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K26" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L26" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M26" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="N26" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O26" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P26" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q26" s="4" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:17">
       <c r="A27" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:17">
       <c r="B28" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H28" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L28" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N28" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N28" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O28" s="4" t="s">
-        <v>199</v>
+        <v>40</v>
       </c>
       <c r="P28" s="4" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="Q28" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
       <c r="B29" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L29" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N29" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P29" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="P29" s="4" t="s">
+      <c r="Q29" s="4" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:17">
       <c r="B30" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H30" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K30" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="L30" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="L30" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="M30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N30" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N30" s="4" t="s">
+      <c r="O30" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="O30" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="P30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q30" s="4" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:17">
       <c r="B31" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G31" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H31" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I31" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J31" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="K31" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L31" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N31" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N31" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O31" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q31" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:17">
       <c r="A32" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
-      <c r="B33" s="1" t="s">
+    <row r="33" spans="1:17">
+      <c r="B33" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F33" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H33" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J33" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K33" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L33" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M33" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N33" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N33" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="O33" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="34" spans="1:16">
-      <c r="B34" s="7" t="s">
+      <c r="Q33" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="B34" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="D34" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F34" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J34" s="6" t="s">
+      <c r="J34" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K34" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K34" s="6" t="s">
+      <c r="L34" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L34" s="6" t="s">
+      <c r="M34" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M34" s="6" t="s">
+      <c r="N34" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="6" t="s">
+      <c r="O34" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="O34" s="6" t="s">
+      <c r="P34" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="P34" s="6" t="s">
+      <c r="Q34" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
-      <c r="B35" s="7" t="s">
+    <row r="35" spans="1:17">
+      <c r="B35" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F35" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H35" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J35" s="6" t="s">
+      <c r="J35" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K35" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K35" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L35" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M35" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N35" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N35" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="O35" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="P35" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="P35" s="6" t="s">
+      <c r="Q35" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
-      <c r="B36" s="1" t="s">
+    <row r="36" spans="1:17">
+      <c r="B36" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="D36" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G36" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H36" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J36" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="K36" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L36" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M36" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N36" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N36" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="O36" s="2" t="s">
         <v>78</v>
       </c>
       <c r="P36" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q36" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:17">
       <c r="A37" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
-      <c r="B38" s="1" t="s">
+    <row r="38" spans="1:17">
+      <c r="B38" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="D38" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F38" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H38" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J38" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K38" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L38" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M38" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N38" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N38" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O38" s="4" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="P38" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="39" spans="1:16">
-      <c r="B39" s="7" t="s">
+      <c r="Q38" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="B39" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="D39" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F39" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H39" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I39" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I39" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J39" s="6" t="s">
+      <c r="J39" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K39" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K39" s="6" t="s">
+      <c r="L39" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L39" s="6" t="s">
+      <c r="M39" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M39" s="6" t="s">
+      <c r="N39" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N39" s="4" t="s">
+      <c r="O39" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="O39" s="4" t="s">
+      <c r="P39" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="P39" s="4" t="s">
+      <c r="Q39" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
-      <c r="B40" s="7" t="s">
+    <row r="40" spans="1:17">
+      <c r="B40" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="D40" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F40" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H40" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J40" s="6" t="s">
+      <c r="J40" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K40" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K40" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L40" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M40" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N40" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N40" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P40" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P40" s="4" t="s">
+      <c r="Q40" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
-      <c r="B41" s="1" t="s">
+    <row r="41" spans="1:17">
+      <c r="B41" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G41" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H41" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J41" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="K41" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K41" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L41" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M41" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N41" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N41" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O41" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P41" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q41" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:17">
       <c r="A42" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
-      <c r="B43" s="1" t="s">
+    <row r="43" spans="1:17">
+      <c r="B43" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="D43" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F43" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H43" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J43" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K43" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K43" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L43" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M43" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N43" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N43" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O43" s="4" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="P43" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="44" spans="1:16">
-      <c r="B44" s="7" t="s">
+      <c r="Q43" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="B44" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C44" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="D44" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H44" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I44" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J44" s="6" t="s">
+      <c r="J44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K44" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K44" s="6" t="s">
+      <c r="L44" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L44" s="6" t="s">
+      <c r="M44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M44" s="6" t="s">
+      <c r="N44" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N44" s="4" t="s">
+      <c r="O44" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="O44" s="4" t="s">
+      <c r="P44" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="P44" s="4" t="s">
+      <c r="Q44" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
-      <c r="B45" s="7" t="s">
+    <row r="45" spans="1:17">
+      <c r="B45" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="D45" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H45" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J45" s="6" t="s">
+      <c r="J45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K45" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K45" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L45" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M45" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N45" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N45" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O45" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P45" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P45" s="4" t="s">
+      <c r="Q45" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
-      <c r="B46" s="1" t="s">
+    <row r="46" spans="1:17">
+      <c r="B46" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="D46" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H46" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I46" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J46" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J46" s="2" t="s">
+      <c r="K46" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K46" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L46" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M46" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N46" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N46" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O46" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P46" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q46" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:17">
       <c r="A47" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
-      <c r="B48" s="1" t="s">
+    <row r="48" spans="1:17">
+      <c r="B48" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="D48" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F48" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H48" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J48" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K48" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K48" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L48" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M48" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N48" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N48" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O48" s="4" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="P48" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="49" spans="1:16">
-      <c r="B49" s="7" t="s">
+      <c r="Q48" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="B49" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C49" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="D49" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="E49" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F49" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H49" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I49" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I49" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J49" s="6" t="s">
+      <c r="J49" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K49" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K49" s="6" t="s">
+      <c r="L49" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L49" s="6" t="s">
+      <c r="M49" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M49" s="6" t="s">
+      <c r="N49" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N49" s="4" t="s">
+      <c r="O49" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="O49" s="4" t="s">
+      <c r="P49" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="P49" s="4" t="s">
+      <c r="Q49" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
-      <c r="B50" s="7" t="s">
+    <row r="50" spans="1:17">
+      <c r="B50" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="D50" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F50" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H50" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J50" s="6" t="s">
+      <c r="J50" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K50" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K50" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L50" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M50" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N50" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N50" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O50" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P50" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P50" s="4" t="s">
+      <c r="Q50" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
-      <c r="B51" s="1" t="s">
+    <row r="51" spans="1:17">
+      <c r="B51" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="D51" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G51" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G51" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H51" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I51" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J51" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="K51" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K51" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L51" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M51" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N51" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N51" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O51" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P51" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q51" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:17">
       <c r="A52" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:17">
       <c r="B53" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="D53" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F53" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H53" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J53" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K53" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K53" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L53" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M53" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N53" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N53" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O53" s="4" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="P53" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="54" spans="1:16">
+      <c r="Q53" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17">
       <c r="B54" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="D54" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="E54" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F54" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G54" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H54" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I54" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I54" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J54" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K54" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K54" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L54" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M54" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N54" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N54" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O54" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P54" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="P54" s="4" t="s">
+      <c r="Q54" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:17">
       <c r="B55" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="D55" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="E55" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F55" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G55" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H55" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J55" s="6" t="s">
+      <c r="J55" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K55" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K55" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L55" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M55" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N55" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N55" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O55" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P55" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P55" s="4" t="s">
+      <c r="Q55" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:17">
       <c r="B56" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="D56" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G56" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H56" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I56" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J56" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J56" s="2" t="s">
+      <c r="K56" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K56" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L56" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M56" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N56" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N56" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O56" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P56" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q56" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:17">
       <c r="A57" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:17">
       <c r="B58" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="D58" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="E58" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F58" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H58" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J58" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K58" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K58" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L58" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M58" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N58" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N58" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O58" s="4" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="P58" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="59" spans="1:16">
+      <c r="Q58" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17">
       <c r="B59" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="D59" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="E59" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F59" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G59" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G59" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H59" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I59" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I59" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J59" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K59" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K59" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L59" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M59" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N59" s="4" t="s">
+      <c r="O59" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="O59" s="4" t="s">
+      <c r="P59" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="P59" s="4" t="s">
+      <c r="Q59" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:17">
       <c r="B60" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="D60" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F60" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G60" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H60" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J60" s="6" t="s">
+      <c r="J60" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K60" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K60" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L60" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M60" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N60" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N60" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O60" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P60" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P60" s="4" t="s">
+      <c r="Q60" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:17">
       <c r="B61" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="D61" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="E61" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F61" s="6" t="s">
+      <c r="F61" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G61" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G61" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H61" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I61" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J61" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J61" s="2" t="s">
+      <c r="K61" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K61" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L61" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M61" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N61" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N61" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O61" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P61" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q61" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:17">
       <c r="A62" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
-      <c r="B63" s="1" t="s">
+    <row r="63" spans="1:17">
+      <c r="B63" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="D63" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="E63" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F63" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G63" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H63" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J63" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K63" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K63" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L63" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M63" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N63" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N63" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O63" s="4" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="P63" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="64" spans="1:16">
-      <c r="B64" s="7" t="s">
+      <c r="Q63" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17">
+      <c r="B64" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C64" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="D64" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F64" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G64" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H64" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I64" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I64" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J64" s="6" t="s">
+      <c r="J64" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K64" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K64" s="6" t="s">
+      <c r="L64" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L64" s="6" t="s">
+      <c r="M64" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M64" s="6" t="s">
+      <c r="N64" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N64" s="4" t="s">
+      <c r="O64" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="O64" s="4" t="s">
+      <c r="P64" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="P64" s="4" t="s">
+      <c r="Q64" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
-      <c r="B65" s="7" t="s">
+    <row r="65" spans="1:17">
+      <c r="B65" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C65" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="D65" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="E65" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F65" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H65" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J65" s="6" t="s">
+      <c r="J65" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K65" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K65" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L65" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M65" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N65" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N65" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O65" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P65" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P65" s="4" t="s">
+      <c r="Q65" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
-      <c r="B66" s="1" t="s">
+    <row r="66" spans="1:17">
+      <c r="B66" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="D66" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F66" s="6" t="s">
+      <c r="F66" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G66" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H66" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I66" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J66" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J66" s="2" t="s">
+      <c r="K66" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K66" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L66" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M66" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N66" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N66" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O66" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P66" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q66" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:17">
       <c r="A67" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
-      <c r="B68" s="1" t="s">
+    <row r="68" spans="1:17">
+      <c r="B68" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="D68" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="E68" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F68" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G68" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G68" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H68" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J68" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K68" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K68" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L68" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M68" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N68" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N68" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O68" s="4" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="P68" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="69" spans="1:16">
-      <c r="B69" s="7" t="s">
+      <c r="Q68" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17">
+      <c r="B69" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="D69" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="E69" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F69" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G69" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G69" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H69" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I69" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I69" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J69" s="6" t="s">
+      <c r="J69" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K69" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K69" s="6" t="s">
+      <c r="L69" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L69" s="6" t="s">
+      <c r="M69" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M69" s="6" t="s">
+      <c r="N69" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N69" s="4" t="s">
+      <c r="O69" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="O69" s="4" t="s">
+      <c r="P69" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="P69" s="4" t="s">
+      <c r="Q69" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:16">
-      <c r="B70" s="7" t="s">
+    <row r="70" spans="1:17">
+      <c r="B70" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="D70" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F70" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G70" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G70" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H70" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J70" s="6" t="s">
+      <c r="J70" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K70" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K70" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L70" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M70" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N70" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N70" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O70" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P70" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P70" s="4" t="s">
+      <c r="Q70" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
-      <c r="B71" s="1" t="s">
+    <row r="71" spans="1:17">
+      <c r="B71" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="D71" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F71" s="6" t="s">
+      <c r="F71" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G71" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G71" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H71" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I71" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J71" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J71" s="2" t="s">
+      <c r="K71" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K71" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L71" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M71" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N71" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N71" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O71" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P71" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q71" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:17">
       <c r="A72" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
-      <c r="B73" s="1" t="s">
+    <row r="73" spans="1:17">
+      <c r="B73" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="D73" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F73" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G73" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H73" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J73" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K73" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K73" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L73" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M73" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N73" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N73" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O73" s="4" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="P73" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="74" spans="1:16">
-      <c r="B74" s="7" t="s">
+      <c r="Q73" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17">
+      <c r="B74" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C74" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="D74" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="E74" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F74" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G74" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H74" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I74" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I74" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J74" s="6" t="s">
+      <c r="J74" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K74" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K74" s="6" t="s">
+      <c r="L74" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L74" s="6" t="s">
+      <c r="M74" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M74" s="6" t="s">
+      <c r="N74" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N74" s="4" t="s">
+      <c r="O74" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="O74" s="4" t="s">
+      <c r="P74" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="P74" s="4" t="s">
+      <c r="Q74" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
-      <c r="B75" s="7" t="s">
+    <row r="75" spans="1:17">
+      <c r="B75" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C75" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="D75" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="E75" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F75" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G75" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H75" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J75" s="6" t="s">
+      <c r="J75" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K75" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K75" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L75" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M75" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N75" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N75" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O75" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P75" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P75" s="4" t="s">
+      <c r="Q75" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
-      <c r="B76" s="1" t="s">
+    <row r="76" spans="1:17">
+      <c r="B76" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="D76" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F76" s="6" t="s">
+      <c r="F76" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G76" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G76" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H76" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I76" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J76" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J76" s="2" t="s">
+      <c r="K76" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K76" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L76" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M76" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N76" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N76" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O76" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P76" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q76" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:17">
       <c r="A77" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
-      <c r="B78" s="1" t="s">
+    <row r="78" spans="1:17">
+      <c r="B78" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="D78" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="E78" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F78" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G78" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G78" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H78" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J78" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K78" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K78" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L78" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M78" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N78" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N78" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O78" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P78" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="P78" s="4" t="s">
+      <c r="Q78" s="4" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
-      <c r="B79" s="7" t="s">
+    <row r="79" spans="1:17">
+      <c r="B79" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C79" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="D79" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="E79" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F79" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H79" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I79" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I79" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J79" s="6" t="s">
+      <c r="J79" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K79" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K79" s="6" t="s">
+      <c r="L79" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L79" s="6" t="s">
+      <c r="M79" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M79" s="6" t="s">
+      <c r="N79" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N79" s="4" t="s">
+      <c r="O79" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="O79" s="4" t="s">
+      <c r="P79" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="P79" s="4" t="s">
+      <c r="Q79" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
-      <c r="B80" s="7" t="s">
+    <row r="80" spans="1:17">
+      <c r="B80" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C80" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="D80" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="E80" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F80" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H80" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J80" s="6" t="s">
+      <c r="J80" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K80" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K80" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L80" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M80" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N80" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N80" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O80" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P80" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P80" s="4" t="s">
+      <c r="Q80" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
-      <c r="B81" s="1" t="s">
+    <row r="81" spans="1:17">
+      <c r="B81" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="D81" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="E81" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F81" s="6" t="s">
+      <c r="F81" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G81" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G81" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H81" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I81" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J81" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J81" s="2" t="s">
+      <c r="K81" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K81" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L81" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M81" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N81" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N81" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O81" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P81" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q81" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:17">
       <c r="A82" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
-      <c r="B83" s="1" t="s">
+    <row r="83" spans="1:17">
+      <c r="B83" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="D83" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="E83" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F83" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G83" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H83" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J83" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K83" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K83" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L83" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M83" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N83" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N83" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O83" s="4" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="P83" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="84" spans="1:16">
-      <c r="B84" s="7" t="s">
+      <c r="Q83" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17">
+      <c r="B84" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C84" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="D84" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="E84" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F84" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G84" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G84" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H84" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I84" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I84" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J84" s="6" t="s">
+      <c r="J84" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K84" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K84" s="6" t="s">
+      <c r="L84" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L84" s="6" t="s">
+      <c r="M84" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M84" s="6" t="s">
+      <c r="N84" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N84" s="4" t="s">
+      <c r="O84" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="O84" s="4" t="s">
+      <c r="P84" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="P84" s="4" t="s">
+      <c r="Q84" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
-      <c r="B85" s="7" t="s">
+    <row r="85" spans="1:17">
+      <c r="B85" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C85" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="D85" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="E85" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F85" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G85" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G85" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H85" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J85" s="6" t="s">
+      <c r="J85" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K85" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K85" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L85" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M85" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N85" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N85" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O85" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P85" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P85" s="4" t="s">
+      <c r="Q85" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
-      <c r="B86" s="1" t="s">
+    <row r="86" spans="1:17">
+      <c r="B86" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="D86" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="E86" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F86" s="6" t="s">
+      <c r="F86" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G86" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G86" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H86" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I86" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J86" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J86" s="2" t="s">
+      <c r="K86" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K86" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L86" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M86" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N86" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N86" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O86" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P86" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q86" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:17">
       <c r="A87" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
-      <c r="B88" s="1" t="s">
+    <row r="88" spans="1:17">
+      <c r="B88" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="D88" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F88" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G88" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G88" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H88" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J88" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K88" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K88" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L88" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M88" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N88" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N88" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O88" s="4" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="P88" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="89" spans="1:16">
-      <c r="B89" s="7" t="s">
+      <c r="Q88" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17">
+      <c r="B89" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C89" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="D89" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="E89" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F89" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G89" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G89" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H89" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I89" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I89" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J89" s="6" t="s">
+      <c r="J89" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K89" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K89" s="6" t="s">
+      <c r="L89" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L89" s="6" t="s">
+      <c r="M89" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M89" s="6" t="s">
+      <c r="N89" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N89" s="4" t="s">
+      <c r="O89" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="O89" s="4" t="s">
+      <c r="P89" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="P89" s="4" t="s">
+      <c r="Q89" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
-      <c r="B90" s="7" t="s">
+    <row r="90" spans="1:17">
+      <c r="B90" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C90" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="D90" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="E90" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F90" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G90" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G90" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H90" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J90" s="6" t="s">
+      <c r="J90" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K90" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K90" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L90" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M90" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N90" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N90" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O90" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P90" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P90" s="4" t="s">
+      <c r="Q90" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
-      <c r="B91" s="1" t="s">
+    <row r="91" spans="1:17">
+      <c r="B91" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="D91" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="E91" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F91" s="6" t="s">
+      <c r="F91" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G91" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G91" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H91" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I91" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J91" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J91" s="2" t="s">
+      <c r="K91" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K91" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L91" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M91" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N91" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N91" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O91" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P91" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q91" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:17">
       <c r="A92" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
-      <c r="B93" s="1" t="s">
+    <row r="93" spans="1:17">
+      <c r="B93" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="D93" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="E93" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F93" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G93" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G93" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H93" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J93" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K93" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K93" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L93" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M93" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N93" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N93" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O93" s="4" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="P93" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="94" spans="1:16">
-      <c r="B94" s="7" t="s">
+      <c r="Q93" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17">
+      <c r="B94" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C94" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="D94" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="E94" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E94" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F94" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G94" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G94" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H94" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I94" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I94" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J94" s="6" t="s">
+      <c r="J94" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K94" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K94" s="6" t="s">
+      <c r="L94" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L94" s="6" t="s">
+      <c r="M94" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M94" s="6" t="s">
+      <c r="N94" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N94" s="4" t="s">
+      <c r="O94" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="O94" s="4" t="s">
+      <c r="P94" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="P94" s="4" t="s">
+      <c r="Q94" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
-      <c r="B95" s="7" t="s">
+    <row r="95" spans="1:17">
+      <c r="B95" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C95" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="D95" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="E95" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F95" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G95" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G95" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H95" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J95" s="6" t="s">
+      <c r="J95" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K95" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K95" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L95" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M95" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N95" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N95" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O95" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P95" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P95" s="4" t="s">
+      <c r="Q95" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
-      <c r="B96" s="1" t="s">
+    <row r="96" spans="1:17">
+      <c r="B96" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="D96" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E96" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F96" s="6" t="s">
+      <c r="F96" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G96" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G96" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H96" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I96" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J96" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J96" s="2" t="s">
+      <c r="K96" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K96" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L96" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M96" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N96" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N96" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="O96" s="4" t="s">
+      <c r="O96" s="8" t="s">
         <v>40</v>
       </c>
       <c r="P96" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q96" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:17">
       <c r="A97" s="4" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:17">
       <c r="B98" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="D98" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="E98" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E98" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F98" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G98" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G98" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H98" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J98" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K98" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K98" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L98" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M98" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N98" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N98" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O98" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P98" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="P98" s="4" t="s">
+      <c r="Q98" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="32">
-      <c r="B99" s="5" t="s">
+    <row r="99" spans="1:17" ht="32">
+      <c r="B99" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C99" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="D99" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="E99" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E99" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F99" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G99" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G99" s="4" t="s">
+      <c r="H99" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H99" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="I99" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J99" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J99" s="4" t="s">
+      <c r="K99" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K99" s="4" t="s">
+      <c r="L99" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="L99" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="M99" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N99" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N99" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O99" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P99" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="P99" s="4" t="s">
+      <c r="Q99" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:17">
       <c r="B100" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C100" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="D100" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="E100" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E100" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F100" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G100" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="H100" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="H100" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="I100" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J100" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K100" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K100" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L100" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M100" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N100" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N100" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O100" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P100" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="P100" s="4" t="s">
+      <c r="Q100" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:17">
       <c r="B101" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C101" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="D101" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="E101" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E101" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="F101" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G101" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G101" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="H101" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J101" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K101" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K101" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="L101" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M101" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N101" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="N101" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O101" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P101" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q101" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:17">
       <c r="A102" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:17">
       <c r="B103" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C103" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="D103" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="E103" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E103" s="6" t="s">
-        <v>76</v>
-      </c>
       <c r="F103" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G103" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G103" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H103" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I103" s="6" t="s">
         <v>76</v>
       </c>
       <c r="J103" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K103" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K103" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="L103" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="M103" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="M103" s="6" t="s">
+      <c r="N103" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="N103" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="O103" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P103" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q103" s="4" t="s">
         <v>225</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="O2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
